--- a/Lio_Events_ICP_Analysis.xlsx
+++ b/Lio_Events_ICP_Analysis.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events Master" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Event Categorization" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Firmographics" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ICP Analysis" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Events Master" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Event Categorization" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Company Firmographics" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ICP Analysis" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Events Master'!$A$1:$X$49</definedName>
@@ -101,7 +101,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -123,11 +123,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -156,6 +200,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -521,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -547,7 +593,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-20 · corrected 2026-08-31</t>
         </is>
       </c>
     </row>
@@ -571,7 +617,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Events Master (all 48 events/appearances) · Event Categorization (counts &amp; funnel logic — formulas live off Events Master) · Company Firmographics (verified table + directional block) · ICP Analysis (pattern synthesis)</t>
+          <t>Events Master (all 49 events/appearances) · Event Categorization (counts &amp; funnel logic — formulas live off Events Master) · Company Firmographics (verified table + directional block) · ICP Analysis (pattern synthesis)</t>
         </is>
       </c>
     </row>
@@ -692,6 +738,16 @@
       <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Walmart = engagement/endorser, not a confirmed customer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Bots &amp; Buyers correction (2026-08-31): the EU flagship was recorded as Sep 23–24 in Munich (presumed, venue TBA). Organizer verification moved it to Oct 27–28 at MotorWorld München — colliding with SIG Chicago (Oct 25–28), not ProcureCon Europe Cologne — and added a separate US edition, Bots &amp; Buyers NYC on Sep 23. See 16-event-status-update.md.</t>
         </is>
       </c>
     </row>
@@ -706,7 +762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X49"/>
+  <dimension ref="A1:X50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1099,7 +1155,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Bots &amp; Buyers — The Summit (EU)</t>
+          <t>Bots &amp; Buyers 2026 EU — The Summit</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -1122,92 +1178,92 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Sep 23–24, 2026</t>
+          <t>Oct 27–28, 2026</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Munich (presumed)</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
+          <t>MotorWorld München (Munich-Freimann)</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>DACH</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>Community summit</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>Confirmed (organizer-verified 2026-08-31)</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>First 2-day edition of the flagship community franchise; billed as "the most AI-focused procurement event on earth"</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="inlineStr">
+        <is>
+          <t>Procurement elite (invite/waitlist)</t>
+        </is>
+      </c>
+      <c r="T4" s="6" t="inlineStr">
+        <is>
           <t>TBA</t>
         </is>
       </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>DACH</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>Community summit</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="O4" s="6" t="inlineStr">
-        <is>
-          <t>Host</t>
-        </is>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>Confirmed (announced)</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>First 2-day edition of the flagship community franchise</t>
-        </is>
-      </c>
-      <c r="S4" s="6" t="inlineStr">
-        <is>
-          <t>Procurement elite (invite/waitlist)</t>
-        </is>
-      </c>
-      <c r="T4" s="6" t="inlineStr">
+      <c r="U4" s="6" t="inlineStr">
         <is>
           <t>TBA</t>
         </is>
       </c>
-      <c r="U4" s="6" t="inlineStr">
+      <c r="V4" s="6" t="inlineStr">
         <is>
           <t>TBA</t>
         </is>
       </c>
-      <c r="V4" s="6" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
       <c r="W4" s="6" t="inlineStr">
         <is>
-          <t>Direct response to #1 attendee complaint about 1-day format; Typeform waitlist live</t>
+          <t>CORRECTED 2026-08-31: previously recorded as Sep 23–24 in Munich (presumed, venue TBA) — organizer verification moved it to Oct 27–28 at MotorWorld München. It therefore COLLIDES with SIG Chicago (Oct 25–28), not with ProcureCon Europe Cologne. Direct response to the #1 attendee complaint about the 1-day format. Excluded from the P1 budget as an own event, but not from the calendar conflict.</t>
         </is>
       </c>
       <c r="X4" s="6" t="inlineStr">
         <is>
-          <t>https://lio.ai/events (waitlist: lio-ai.typeform.com/to/OokcaKa0)</t>
+          <t>https://bots-and-buyers-eu.lio.ai/</t>
         </is>
       </c>
     </row>
@@ -6518,6 +6574,124 @@
       <c r="X49" s="7" t="inlineStr">
         <is>
           <t>https://conference.dpw.ai/awards/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Bots &amp; Buyers NYC 2026</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Bots &amp; Buyers</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>Own community flagship</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>Lio</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>Sep 23, 2026</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="L50" s="6" t="inlineStr">
+        <is>
+          <t>Community summit</t>
+        </is>
+      </c>
+      <c r="M50" s="6" t="inlineStr">
+        <is>
+          <t>In-person</t>
+        </is>
+      </c>
+      <c r="N50" s="6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="O50" s="6" t="inlineStr">
+        <is>
+          <t>Host</t>
+        </is>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>Confirmed (organizer-verified 2026-08-31)</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>First US edition of the flagship community franchise — free and application-only: live agents, trainings, CPO panels, the Lio Awards</t>
+        </is>
+      </c>
+      <c r="S50" s="6" t="inlineStr">
+        <is>
+          <t>500+ curated procurement leaders (application-only)</t>
+        </is>
+      </c>
+      <c r="T50" s="6" t="inlineStr">
+        <is>
+          <t>500+ (curated)</t>
+        </is>
+      </c>
+      <c r="U50" s="6" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="V50" s="6" t="inlineStr">
+        <is>
+          <t>TBA (US pod — Petras)</t>
+        </is>
+      </c>
+      <c r="W50" s="6" t="inlineStr">
+        <is>
+          <t>Lands MID-GAUNTLET between ProcureCon Europe Cologne (Sep 22–24) and ProcureCon East Boston (Sep 28–30) — it competes for the US pod, not the DACH squad. Added 2026-08-31 on organizer verification; the franchise went transatlantic after this workbook was compiled.</t>
+        </is>
+      </c>
+      <c r="X50" s="6" t="inlineStr">
+        <is>
+          <t>https://lio.ai/events</t>
         </is>
       </c>
     </row>
@@ -6558,6 +6732,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -6617,7 +6792,7 @@
         </is>
       </c>
       <c r="F5" s="7">
-        <f>COUNTIF('Events Master'!$D$2:$D$49,A5)</f>
+        <f>COUNTIF('Events Master'!$D$2:$D$50,A5)</f>
         <v/>
       </c>
     </row>
@@ -6648,7 +6823,7 @@
         </is>
       </c>
       <c r="F6" s="6">
-        <f>COUNTIF('Events Master'!$D$2:$D$49,A6)</f>
+        <f>COUNTIF('Events Master'!$D$2:$D$50,A6)</f>
         <v/>
       </c>
     </row>
@@ -6679,7 +6854,7 @@
         </is>
       </c>
       <c r="F7" s="7">
-        <f>COUNTIF('Events Master'!$D$2:$D$49,A7)</f>
+        <f>COUNTIF('Events Master'!$D$2:$D$50,A7)</f>
         <v/>
       </c>
     </row>
@@ -6710,7 +6885,7 @@
         </is>
       </c>
       <c r="F8" s="6">
-        <f>COUNTIF('Events Master'!$D$2:$D$49,A8)</f>
+        <f>COUNTIF('Events Master'!$D$2:$D$50,A8)</f>
         <v/>
       </c>
     </row>
@@ -6741,7 +6916,7 @@
         </is>
       </c>
       <c r="F9" s="7">
-        <f>COUNTIF('Events Master'!$D$2:$D$49,A9)</f>
+        <f>COUNTIF('Events Master'!$D$2:$D$50,A9)</f>
         <v/>
       </c>
     </row>
@@ -6772,7 +6947,7 @@
         </is>
       </c>
       <c r="F10" s="6">
-        <f>COUNTIF('Events Master'!$D$2:$D$49,A10)</f>
+        <f>COUNTIF('Events Master'!$D$2:$D$50,A10)</f>
         <v/>
       </c>
     </row>
@@ -6803,7 +6978,7 @@
         </is>
       </c>
       <c r="F11" s="7">
-        <f>COUNTIF('Events Master'!$D$2:$D$49,A11)</f>
+        <f>COUNTIF('Events Master'!$D$2:$D$50,A11)</f>
         <v/>
       </c>
     </row>
@@ -6834,7 +7009,7 @@
         </is>
       </c>
       <c r="F12" s="6">
-        <f>COUNTIF('Events Master'!$D$2:$D$49,A12)</f>
+        <f>COUNTIF('Events Master'!$D$2:$D$50,A12)</f>
         <v/>
       </c>
     </row>
@@ -6865,7 +7040,7 @@
         </is>
       </c>
       <c r="F13" s="7">
-        <f>COUNTIF('Events Master'!$D$2:$D$49,A13)</f>
+        <f>COUNTIF('Events Master'!$D$2:$D$50,A13)</f>
         <v/>
       </c>
     </row>
@@ -6896,7 +7071,7 @@
         </is>
       </c>
       <c r="F14" s="6">
-        <f>COUNTIF('Events Master'!$D$2:$D$49,A14)</f>
+        <f>COUNTIF('Events Master'!$D$2:$D$50,A14)</f>
         <v/>
       </c>
     </row>
@@ -6911,6 +7086,7 @@
         <v/>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
@@ -6925,7 +7101,7 @@
         </is>
       </c>
       <c r="B18">
-        <f>COUNTIF('Events Master'!$K$2:$K$49,A18)</f>
+        <f>COUNTIF('Events Master'!$K$2:$K$50,A18)</f>
         <v/>
       </c>
     </row>
@@ -6936,7 +7112,7 @@
         </is>
       </c>
       <c r="B19">
-        <f>COUNTIF('Events Master'!$K$2:$K$49,A19)</f>
+        <f>COUNTIF('Events Master'!$K$2:$K$50,A19)</f>
         <v/>
       </c>
     </row>
@@ -6947,7 +7123,7 @@
         </is>
       </c>
       <c r="B20">
-        <f>COUNTIF('Events Master'!$K$2:$K$49,A20)</f>
+        <f>COUNTIF('Events Master'!$K$2:$K$50,A20)</f>
         <v/>
       </c>
     </row>
@@ -6958,7 +7134,7 @@
         </is>
       </c>
       <c r="B21">
-        <f>COUNTIF('Events Master'!$K$2:$K$49,A21)</f>
+        <f>COUNTIF('Events Master'!$K$2:$K$50,A21)</f>
         <v/>
       </c>
     </row>
@@ -6969,10 +7145,11 @@
         </is>
       </c>
       <c r="B22">
-        <f>COUNTIF('Events Master'!$K$2:$K$49,A22)</f>
+        <f>COUNTIF('Events Master'!$K$2:$K$50,A22)</f>
         <v/>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
@@ -6987,7 +7164,7 @@
         </is>
       </c>
       <c r="B25">
-        <f>COUNTIF('Events Master'!$F$2:$F$49,2023)</f>
+        <f>COUNTIF('Events Master'!$F$2:$F$50,2023)</f>
         <v/>
       </c>
     </row>
@@ -6998,7 +7175,7 @@
         </is>
       </c>
       <c r="B26">
-        <f>COUNTIF('Events Master'!$F$2:$F$49,2024)</f>
+        <f>COUNTIF('Events Master'!$F$2:$F$50,2024)</f>
         <v/>
       </c>
     </row>
@@ -7009,7 +7186,7 @@
         </is>
       </c>
       <c r="B27">
-        <f>COUNTIF('Events Master'!$F$2:$F$49,2025)</f>
+        <f>COUNTIF('Events Master'!$F$2:$F$50,2025)</f>
         <v/>
       </c>
     </row>
@@ -7020,10 +7197,11 @@
         </is>
       </c>
       <c r="B28">
-        <f>COUNTIF('Events Master'!$F$2:$F$49,2026)</f>
+        <f>COUNTIF('Events Master'!$F$2:$F$50,2026)</f>
         <v/>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
@@ -7038,7 +7216,7 @@
         </is>
       </c>
       <c r="B31">
-        <f>COUNTIF('Events Master'!$P$2:$P$49,A31)</f>
+        <f>COUNTIF('Events Master'!$P$2:$P$50,A31)</f>
         <v/>
       </c>
     </row>
@@ -7049,7 +7227,7 @@
         </is>
       </c>
       <c r="B32">
-        <f>COUNTIF('Events Master'!$P$2:$P$49,A32)</f>
+        <f>COUNTIF('Events Master'!$P$2:$P$50,A32)</f>
         <v/>
       </c>
     </row>
@@ -7060,10 +7238,11 @@
         </is>
       </c>
       <c r="B33">
-        <f>COUNTIF('Events Master'!$P$2:$P$49,A33)</f>
+        <f>COUNTIF('Events Master'!$P$2:$P$50,A33)</f>
         <v/>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
@@ -9240,8 +9419,6 @@
           <t>Why it matters / audience</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
@@ -9254,6 +9431,8 @@
           <t>13,000-member German association; ~1,000 at eLösungstage; the DACH operating layer (heads-of + managers). Lio: exhibitor 2025 → official partner 2026 + award 2024 + sidecar dinner</t>
         </is>
       </c>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="17" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
@@ -9266,6 +9445,8 @@
           <t>1,700–2,500 digital-procurement decision-makers, CPO/VP-heavy, €2.2K ticket; the transformation elite + VC/vendor ecosystem. Lio: 2025 award winner, 2026 NY sponsor+booth+speaker</t>
         </is>
       </c>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="17" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
@@ -9278,6 +9459,8 @@
           <t>~150–250 German C-levels, €2.5K, Chatham House; highest CPO density in DE. Lio: calendar-listed sponsor + 2 placed articles</t>
         </is>
       </c>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="17" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
@@ -9290,6 +9473,8 @@
           <t>US indirect-procurement establishment, majority director+; Lio escalated to LEAD sponsor at East 2026 alongside SAP/Coupa/GEP</t>
         </is>
       </c>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="17" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
@@ -9302,6 +9487,8 @@
           <t>GBS/SSC/BPO buyers — the audience that owns the BPO line item Lio attacks ('Your BPO Costs 93% Too Much')</t>
         </is>
       </c>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="17" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
@@ -9314,6 +9501,8 @@
           <t>Most senior peer network; 70% director+; membership-gated ABM</t>
         </is>
       </c>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="17" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
@@ -9326,6 +9515,8 @@
           <t>~2,300 German practitioners; 3 consecutive years of Keil on stage — mid-market + enterprise DACH reach</t>
         </is>
       </c>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="17" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
@@ -9338,6 +9529,8 @@
           <t>The conversion layer: aggregate the above audiences into owned rooms (150→300 people; 2-day Summit Sep 2026)</t>
         </is>
       </c>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="17" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
